--- a/uCodeRev7.5.3.1.xlsx
+++ b/uCodeRev7.5.3.1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED0904D-5976-4EB9-94B8-3C61CEDEF42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2E7B1208-AD10-4BE6-B85C-04552331AAA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{2E7B1208-AD10-4BE6-B85C-04552331AAA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Ops" sheetId="11" r:id="rId1"/>
@@ -3153,6 +3153,10 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3174,10 +3178,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3561,7 +3561,7 @@
       <c r="R1" s="97" t="s">
         <v>182</v>
       </c>
-      <c r="S1" s="137" t="s">
+      <c r="S1" s="130" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4533,18 +4533,18 @@
       <c r="N1" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="127" t="s">
+      <c r="O1" s="131" t="s">
         <v>562</v>
       </c>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="129"/>
-      <c r="Z1" s="127" t="s">
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="133"/>
+      <c r="Z1" s="131" t="s">
         <v>498</v>
       </c>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="128"/>
-      <c r="AC1" s="129"/>
+      <c r="AA1" s="132"/>
+      <c r="AB1" s="132"/>
+      <c r="AC1" s="133"/>
     </row>
     <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="107"/>
@@ -4593,10 +4593,10 @@
         <v>50</v>
       </c>
       <c r="R2" s="111"/>
-      <c r="Z2" s="134"/>
-      <c r="AA2" s="135"/>
-      <c r="AB2" s="135"/>
-      <c r="AC2" s="136"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="128"/>
+      <c r="AB2" s="128"/>
+      <c r="AC2" s="129"/>
     </row>
     <row r="3" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="112" t="s">
@@ -4608,25 +4608,25 @@
       <c r="C3" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="130"/>
-      <c r="F3" s="131" t="s">
+      <c r="E3" s="134"/>
+      <c r="F3" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="132"/>
-      <c r="H3" s="130" t="s">
+      <c r="G3" s="136"/>
+      <c r="H3" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="133" t="s">
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="137" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="132"/>
+      <c r="N3" s="136"/>
       <c r="O3" s="114" t="s">
         <v>37</v>
       </c>
